--- a/MDA/demo_mda_9999_1_location.xlsx
+++ b/MDA/demo_mda_9999_1_location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\MDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA987D2B-C034-4B09-9E27-0664CFCDD004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1461E11-F718-4000-BBA6-357F63C1053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -295,9 +295,6 @@
     <t>l_eligible_pop</t>
   </si>
   <si>
-    <t>. &lt; ${l_total_pop}</t>
-  </si>
-  <si>
     <t>The eligible population cannot exceed the total population</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>l_start</t>
+  </si>
+  <si>
+    <t>. &lt;= ${l_total_pop}</t>
   </si>
 </sst>
 </file>
@@ -806,7 +806,7 @@
         <v>27</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O1" s="13" t="s">
         <v>21</v>
@@ -877,7 +877,7 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P3" s="15" t="s">
         <v>25</v>
@@ -938,7 +938,7 @@
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q5" s="15" t="s">
         <v>25</v>
@@ -971,7 +971,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
       <c r="Q6" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R6" s="15" t="s">
         <v>25</v>
@@ -1018,10 +1018,10 @@
       <c r="D8" s="14"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>86</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>87</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9"/>
@@ -1042,14 +1042,14 @@
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="14"/>
@@ -1072,7 +1072,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>33</v>
@@ -1100,7 +1100,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>34</v>
@@ -1112,7 +1112,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
